--- a/initial solution/rule-based-final/small_scale_v2 copy/online_schedule_seed1.xlsx
+++ b/initial solution/rule-based-final/small_scale_v2 copy/online_schedule_seed1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,7 +573,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -591,22 +591,22 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>S9</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>675</v>
+        <v>710</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P27</t>
+          <t>P28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>sleep apnea diagnosis test</t>
+          <t>excision of the lymphadenopathy from the lumbar</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -614,102 +614,102 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>S7</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>S9</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>710</v>
+        <v>790</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>buccal mucosa bioppsy</t>
+          <t>excision of the lymphadenopathy from the lumbar</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>S2</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>S5</t>
-        </is>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>S10</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>755</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P28</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>excision of the lymphadenopathy from the lumbar</t>
+          <t>buccal mucosa bioppsy</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -718,26 +718,26 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>755</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P23</t>
+          <t>P25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>septoplasty</t>
+          <t>buccal mucosa bioppsy</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -745,27 +745,27 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>S7</t>
+          <t>S6</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S11</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>800</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P32</t>
+          <t>P26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -786,7 +786,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -796,43 +796,43 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>S9</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>800</v>
+        <v>2180</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>buccal mucosa bioppsy</t>
+          <t>endoscopic sinus</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>S6</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -841,18 +841,18 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>870</v>
+        <v>2185</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P21</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>excision of the lymphadenopathy from the lumbar</t>
+          <t>microlaryngoscopy</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -860,11 +860,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -878,22 +878,22 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>S11</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2095</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P25</t>
+          <t>P35</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>buccal mucosa bioppsy</t>
+          <t>endoscopic sinus</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -909,32 +909,32 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>S6</t>
+          <t>S5</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>S9</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2140</v>
+        <v>2265</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P34</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>endoscopic sinus</t>
+          <t>excision of the lymphadenopathy from the lumbar</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -942,56 +942,56 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>S7</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>S6</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S9</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2185</v>
+        <v>2335</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P26</t>
+          <t>P20</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>adenotonsillectomy</t>
+          <t>excision of the lymphadenopathy from the lumbar</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1001,30 +1001,30 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S9</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2185</v>
+        <v>3475</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P21</t>
+          <t>P15</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>microlaryngoscopy</t>
+          <t>sleep apnea diagnosis test</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1032,12 +1032,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S7</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1046,26 +1046,26 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2260</v>
+        <v>3530</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P34</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>excision of the lymphadenopathy from the lumbar</t>
+          <t>adenotonsillectomy</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -1078,76 +1078,76 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>S9</t>
+          <t>S11</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2340</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P20</t>
+          <t>P22</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>excision of the lymphadenopathy from the lumbar</t>
+          <t>endoscopic sinus</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>S8</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S6</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2350</v>
+        <v>3720</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P15</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>sleep apnea diagnosis test</t>
+          <t>rhinoplasty</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1155,81 +1155,81 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S7</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>S7</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>S9</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3530</v>
+        <v>4990</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P5</t>
+          <t>P29</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>adenotonsillectomy</t>
+          <t>modified radical mastoidectomy</t>
         </is>
       </c>
       <c r="C19" t="n">
+        <v>3</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
         <v>2</v>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>11:31</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>1</v>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>S5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S9</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3571</v>
+        <v>4990</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P33</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>modified radical mastoidectomy</t>
+          <t>septoplasty</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1237,40 +1237,40 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>S7</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3646</v>
+        <v>5120</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P22</t>
+          <t>P8</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>endoscopic sinus</t>
+          <t>modified radical mastoidectomy</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -1278,122 +1278,114 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>S7</t>
+          <t>S6</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>S6</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S11</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3720</v>
+        <v>10830</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P29</t>
+          <t>P18</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>modified radical mastoidectomy</t>
+          <t>endoscopic sinus</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>S7</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>S4</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>S10</t>
-        </is>
-      </c>
+          <t>S6</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>4990</v>
+        <v>10960</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P19</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>septoplasty</t>
+          <t>thyroidectomy</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
           <t>S4</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>S7</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>S11</t>
-        </is>
-      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>5120</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>P14</t>
+          <t>P16</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>modified radical mastoidectomy</t>
+          <t>septoplasty</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -1401,44 +1393,40 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>S3</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
+          <t>S8</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>5120</v>
+        <v>12175</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P30</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>modified radical mastoidectomy</t>
+          <t>thyroidectomy</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1450,32 +1438,28 @@
           <t>S4</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>S9</t>
-        </is>
-      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>10830</v>
+        <v>12190</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>P18</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>endoscopic sinus</t>
+          <t>sleep apnea diagnosis test</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1483,32 +1467,32 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>S7</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>S6</t>
+          <t>S8</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>S9</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>10960</v>
+        <v>12281</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>P19</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>thyroidectomy</t>
+          <t>microlaryngoscopy</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1516,7 +1500,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -1524,36 +1508,40 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>S4</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>12000</v>
+        <v>12380</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>P16</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>septoplasty</t>
+          <t>thyroidectomy</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -1561,27 +1549,23 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>S5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>S7</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>S11</t>
-        </is>
-      </c>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
-        <v>12190</v>
+        <v>13440</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>P30</t>
+          <t>P31</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1590,7 +1574,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1598,11 +1582,11 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>S6</t>
+          <t>S5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1612,162 +1596,6 @@
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
-        <v>12190</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>sleep apnea diagnosis test</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>8</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>12:56</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>1</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>S7</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>S10</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>12296</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>microlaryngoscopy</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>8</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>1</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>S4</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="n">
-        <v>12380</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>thyroidectomy</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>9</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>S6</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>S10</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
-        <v>13440</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>P31</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>thyroidectomy</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>9</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>2</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>S5</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="n">
         <v>13630</v>
       </c>
     </row>
